--- a/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0002T0006Z000C1N46_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0002T0006Z000C1N46_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>22.95227615505311</v>
+        <v>3.729744875196131</v>
       </c>
       <c r="D2" t="n">
-        <v>22.68582038467821</v>
+        <v>3.686445812510209</v>
       </c>
       <c r="E2" t="n">
-        <v>5.672320978064588</v>
+        <v>0.9217521589354957</v>
       </c>
       <c r="F2" t="n">
-        <v>4.829231784401808</v>
+        <v>0.7847501649652937</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>9.691693204742823</v>
+        <v>1.574900145770709</v>
       </c>
       <c r="D3" t="n">
-        <v>12.83431894483607</v>
+        <v>2.08557682853586</v>
       </c>
       <c r="E3" t="n">
-        <v>5.672320978064588</v>
+        <v>0.9217521589354957</v>
       </c>
       <c r="F3" t="n">
-        <v>4.829231784401808</v>
+        <v>0.7847501649652937</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>12.72946208215174</v>
+        <v>2.068537588349658</v>
       </c>
       <c r="D4" t="n">
-        <v>12.08930270964109</v>
+        <v>1.964511690316677</v>
       </c>
       <c r="E4" t="n">
-        <v>5.672320978064588</v>
+        <v>0.9217521589354957</v>
       </c>
       <c r="F4" t="n">
-        <v>4.829231784401808</v>
+        <v>0.7847501649652937</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
